--- a/public/exports-with-coowners/29189714.xlsx
+++ b/public/exports-with-coowners/29189714.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054009</t>
+          <t xml:space="preserve">200054021</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311240209</t>
+          <t xml:space="preserve">311240221</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">

--- a/public/exports-with-coowners/29189714.xlsx
+++ b/public/exports-with-coowners/29189714.xlsx
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054021</t>
+          <t xml:space="preserve">200054009</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023290</t>
+          <t xml:space="preserve">310023291</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023290</t>
+          <t xml:space="preserve">310023291</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4504,12 +4504,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports-with-coowners/29189714.xlsx
+++ b/public/exports-with-coowners/29189714.xlsx
@@ -3364,7 +3364,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023291</t>
+          <t xml:space="preserve">310023290</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">310023291</t>
+          <t xml:space="preserve">310023290</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311240221</t>
+          <t xml:space="preserve">311240209</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
